--- a/A重量运费重制版.xlsx
+++ b/A重量运费重制版.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\myfirstgithubcode\daiyujinweb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59D93172-5F83-4AA1-B867-CA4E74FA3986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C5893CC-17D5-4166-96FC-ADABA249D506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1027,9 +1027,6 @@
           <cell r="A247" t="str">
             <v>日本</v>
           </cell>
-          <cell r="C247">
-            <v>5</v>
-          </cell>
         </row>
         <row r="248">
           <cell r="A248" t="str">
@@ -1066,9 +1063,6 @@
         <row r="252">
           <cell r="A252" t="str">
             <v>德国</v>
-          </cell>
-          <cell r="C252">
-            <v>16</v>
           </cell>
         </row>
         <row r="253">
@@ -1187,9 +1181,6 @@
           <cell r="A273" t="str">
             <v>日本</v>
           </cell>
-          <cell r="C273">
-            <v>34</v>
-          </cell>
         </row>
         <row r="274">
           <cell r="A274" t="str">
@@ -1226,9 +1217,6 @@
         <row r="278">
           <cell r="A278" t="str">
             <v>德国</v>
-          </cell>
-          <cell r="C278">
-            <v>65</v>
           </cell>
         </row>
         <row r="279">
@@ -2869,6 +2857,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BJ297"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:62" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -57149,28 +57140,27 @@
         <v>3</v>
       </c>
       <c r="C248" s="10">
-        <f>[1]区域运费FedEX!C247</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D248" s="11">
         <f>H248/7</f>
-        <v>119.03142857142858</v>
+        <v>207.9</v>
       </c>
       <c r="E248" s="11">
         <f>H248/6</f>
-        <v>138.87</v>
+        <v>242.54999999999998</v>
       </c>
       <c r="F248" s="10">
         <f>IF(C248&lt;=5,C248+1,IF(C248&lt;=10,C248+2,IF(C248&lt;=16,C248+3,IF(C248&lt;=20,20,IF(C248&lt;=26,C248-10+3,IF(C248&lt;=33,20,IF(C248&lt;=70,C248+7.5,IF(C248&lt;=300,C248+12.5,C248+22))))))))</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G248" s="9" t="str" cm="1">
         <f t="array" ref="G248">INDEX(C$2:BJ$234,MATCH(A248,A$2:A$234,0),MATCH(F248,C$1:BJ$1,0))</f>
-        <v>462.90</v>
+        <v>808.50</v>
       </c>
       <c r="H248" s="9">
         <f>G248*H$247</f>
-        <v>833.22</v>
+        <v>1455.3</v>
       </c>
       <c r="I248" s="5"/>
       <c r="J248" s="5"/>
@@ -57589,28 +57579,27 @@
         <v>7</v>
       </c>
       <c r="C253" s="10">
-        <f>[1]区域运费FedEX!C252</f>
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D253" s="11">
         <f t="shared" si="1"/>
-        <v>489.93428571428569</v>
+        <v>194.01428571428573</v>
       </c>
       <c r="E253" s="11">
         <f t="shared" si="2"/>
-        <v>571.59</v>
+        <v>226.35000000000002</v>
       </c>
       <c r="F253" s="10">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="G253" s="9" t="str" cm="1">
         <f t="array" ref="G253">INDEX(C$2:BJ$234,MATCH(A253,A$2:A$234,0),MATCH(F253,C$1:BJ$1,0))</f>
-        <v>1,905.30</v>
+        <v>754.50</v>
       </c>
       <c r="H253" s="9">
         <f t="shared" si="4"/>
-        <v>3429.54</v>
+        <v>1358.1000000000001</v>
       </c>
       <c r="I253" s="5"/>
       <c r="J253" s="5"/>
@@ -59313,28 +59302,27 @@
         <v>3区</v>
       </c>
       <c r="C274" s="17">
-        <f>[1]区域运费FedEX!C273</f>
-        <v>34</v>
+        <v>123</v>
       </c>
       <c r="D274" s="11">
         <f>H274*F274/7</f>
-        <v>211.75078571428571</v>
+        <v>817.08435714285713</v>
       </c>
       <c r="E274" s="11">
         <f>H274*F274/6</f>
-        <v>247.04258333333334</v>
+        <v>953.26508333333334</v>
       </c>
       <c r="F274" s="18">
         <f>IF(C274&lt;=33,"",IF(C274&lt;=70,C274+7.5,IF(C274&lt;=300,C274+12.5,C274*1.0822)))</f>
-        <v>41.5</v>
+        <v>135.5</v>
       </c>
       <c r="G274" s="9">
         <f>INDEX(B$236:J$244,MATCH(IF(F274&lt;=70,"30.1-70",IF(F274&lt;=300,"70.1-300","300.1-999")),A$236:A$244,0),MATCH(B274,B$235:J$235,0))+CHOOSE(B248,0.8,0.8,0.8,0.8,2.3,13.7,15.8,11.7,11.7)-CHOOSE(B248,0.8,0.8,0.8,0.8,2.3,13.7,15.8,11.7,11.7)</f>
-        <v>21.01</v>
+        <v>24.83</v>
       </c>
       <c r="H274" s="9">
         <f>G274*H$273+CHOOSE(B248,0.8,0.8,0.8,0.8,2.3,13.7,15.8,11.7,11.7)-CHOOSE(B248,0.8,0.8,0.8,0.8,2.3,13.7,15.8,11.7,11.7)</f>
-        <v>35.716999999999999</v>
+        <v>42.210999999999999</v>
       </c>
       <c r="I274" s="5"/>
       <c r="J274" s="13"/>
@@ -59753,20 +59741,19 @@
         <v>7区</v>
       </c>
       <c r="C279" s="17">
-        <f>[1]区域运费FedEX!C278</f>
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="D279" s="11">
         <f t="shared" si="6"/>
-        <v>802.88571428571436</v>
+        <v>1024.3714285714289</v>
       </c>
       <c r="E279" s="11">
         <f t="shared" si="7"/>
-        <v>936.70000000000016</v>
+        <v>1195.1000000000001</v>
       </c>
       <c r="F279" s="18">
         <f t="shared" si="8"/>
-        <v>72.5</v>
+        <v>92.5</v>
       </c>
       <c r="G279" s="9">
         <f t="shared" si="9"/>
